--- a/artfynd/A 33825-2023 artfynd.xlsx
+++ b/artfynd/A 33825-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33825-2023 artfynd.xlsx
+++ b/artfynd/A 33825-2023 artfynd.xlsx
@@ -1238,12 +1238,7 @@
         <v>113161462</v>
       </c>
       <c r="B7" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,11 +1263,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>äldre spillning</t>
